--- a/pages/video_analysis/TP_Master_Women.xlsx
+++ b/pages/video_analysis/TP_Master_Women.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\video_analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFEF063E-F4DB-4417-95EA-CB3F8B5A66E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C9575BB-9571-470C-9D11-59055C165370}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/pages/video_analysis/TP_Master_Women.xlsx
+++ b/pages/video_analysis/TP_Master_Women.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\video_analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BD45FA3-636B-4608-96C5-1618DB81D29B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B5DB6BC-EEEC-4A12-BA74-CA831C3CB8CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15957,7 +15957,7 @@
         <v>56.818181818181287</v>
       </c>
       <c r="H522" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I522" t="s">
         <v>42</v>

--- a/pages/video_analysis/TP_Master_Women.xlsx
+++ b/pages/video_analysis/TP_Master_Women.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\video_analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B5DB6BC-EEEC-4A12-BA74-CA831C3CB8CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CE43990-9E8B-4F9C-896B-F65D305FD85F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -10554,7 +10554,7 @@
         <v>58.593749999997783</v>
       </c>
       <c r="H336" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I336" t="s">
         <v>35</v>

--- a/pages/video_analysis/TP_Master_Women.xlsx
+++ b/pages/video_analysis/TP_Master_Women.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\video_analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37453AD8-9315-44CC-9FA6-444B20FEB9D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94738872-6C34-4F27-BA81-BD291F72685A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1968" yWindow="3120" windowWidth="13824" windowHeight="7260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8056" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8057" uniqueCount="152">
   <si>
     <t>Title</t>
   </si>
@@ -474,6 +474,9 @@
   <si>
     <t>https://youtu.be/36hx4KwX5BQ</t>
   </si>
+  <si>
+    <t>https://youtu.be/Avfxp8hqo2Q</t>
+  </si>
 </sst>
 </file>
 
@@ -76376,7 +76379,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="2609" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2609" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2609" t="s">
         <v>55</v>
       </c>
@@ -76405,7 +76408,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="2610" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2610" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2610" t="s">
         <v>55</v>
       </c>
@@ -76434,7 +76437,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="2611" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2611" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2611" t="s">
         <v>55</v>
       </c>
@@ -76463,7 +76466,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="2612" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2612" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2612" t="s">
         <v>55</v>
       </c>
@@ -76492,7 +76495,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="2613" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2613" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2613" t="s">
         <v>55</v>
       </c>
@@ -76521,7 +76524,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="2614" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2614" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2614" t="s">
         <v>55</v>
       </c>
@@ -76550,7 +76553,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="2615" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2615" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2615" t="s">
         <v>56</v>
       </c>
@@ -76578,8 +76581,11 @@
       <c r="I2615" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="2616" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J2615" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="2616" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2616" t="s">
         <v>56</v>
       </c>
@@ -76608,7 +76614,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="2617" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2617" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2617" t="s">
         <v>56</v>
       </c>
@@ -76637,7 +76643,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="2618" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2618" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2618" t="s">
         <v>56</v>
       </c>
@@ -76666,7 +76672,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="2619" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2619" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2619" t="s">
         <v>56</v>
       </c>
@@ -76695,7 +76701,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="2620" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2620" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2620" t="s">
         <v>56</v>
       </c>
@@ -76724,7 +76730,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="2621" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2621" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2621" t="s">
         <v>56</v>
       </c>
@@ -76753,7 +76759,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="2622" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2622" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2622" t="s">
         <v>56</v>
       </c>
@@ -76782,7 +76788,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="2623" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2623" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2623" t="s">
         <v>56</v>
       </c>
@@ -76811,7 +76817,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="2624" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2624" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2624" t="s">
         <v>56</v>
       </c>
